--- a/data/trans_orig/P55$nadie-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P55$nadie-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>837</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11199</t>
+          <t>9318</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2607</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11535</t>
+          <t>12395</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5138</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17189</t>
+          <t>16751</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,31%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16125</t>
+          <t>15992</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28839</t>
+          <t>28477</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10924</t>
+          <t>10551</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24794</t>
+          <t>24361</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29540</t>
+          <t>30043</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48661</t>
+          <t>49273</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>45,02%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10953</t>
+          <t>11297</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>5646</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17034</t>
+          <t>17116</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10183</t>
+          <t>9198</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>24777</t>
+          <t>24718</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13998</t>
+          <t>13464</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>8294</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20604</t>
+          <t>20468</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13156</t>
+          <t>13566</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29645</t>
+          <t>30409</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,78%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4227</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1669</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10104</t>
+          <t>9344</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1877</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11074</t>
+          <t>11290</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>803</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7210</t>
+          <t>6945</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10109</t>
+          <t>9992</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23267</t>
+          <t>23090</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11856</t>
+          <t>12003</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>26515</t>
+          <t>27101</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,76%</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3511</t>
+          <t>4284</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6769</t>
+          <t>5633</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>826</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7434</t>
+          <t>7239</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>912</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7770</t>
+          <t>7904</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>4196</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16914</t>
+          <t>16468</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5687</t>
+          <t>6521</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20082</t>
+          <t>20773</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30708</t>
+          <t>31253</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48276</t>
+          <t>48368</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3474</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14927</t>
+          <t>15338</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2030,12 +2030,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>36067</t>
+          <t>36151</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>60709</t>
+          <t>60982</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -2093,12 +2093,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8475</t>
+          <t>8336</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21697</t>
+          <t>21834</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47198</t>
+          <t>47122</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>73782</t>
+          <t>73619</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58272</t>
+          <t>59957</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>88200</t>
+          <t>89566</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>36,11%</t>
         </is>
       </c>
     </row>
@@ -2206,12 +2206,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10851</t>
+          <t>10821</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24840</t>
+          <t>25232</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2221,12 +2221,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,12 +2241,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34016</t>
+          <t>34216</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57900</t>
+          <t>57564</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2256,12 +2256,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>50064</t>
+          <t>49847</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>78270</t>
+          <t>77862</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,39%</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>6923</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6830</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8439</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -2432,12 +2432,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7295</t>
+          <t>7148</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19699</t>
+          <t>19438</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24564</t>
+          <t>24520</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>47308</t>
+          <t>46868</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,12 +2502,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34931</t>
+          <t>34390</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61087</t>
+          <t>60813</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,52%</t>
         </is>
       </c>
     </row>
@@ -2580,12 +2580,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3337</t>
+          <t>3365</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15730</t>
+          <t>16258</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,12 +2615,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>3342</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14660</t>
+          <t>14487</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5381</t>
+          <t>5626</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6677</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7036</t>
+          <t>4739</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6775</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3001,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2724</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13387</t>
+          <t>14318</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8557</t>
+          <t>8471</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23850</t>
+          <t>23526</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3051,12 +3051,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13473</t>
+          <t>14130</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>31810</t>
+          <t>32718</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -3114,12 +3114,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>51690</t>
+          <t>49719</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>72241</t>
+          <t>73993</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3129,12 +3129,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16649</t>
+          <t>16892</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34700</t>
+          <t>35436</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3164,12 +3164,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>70432</t>
+          <t>71300</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>104258</t>
+          <t>103352</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3199,12 +3199,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>28,91%</t>
         </is>
       </c>
     </row>
@@ -3227,12 +3227,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12583</t>
+          <t>12479</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>28630</t>
+          <t>28676</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>56279</t>
+          <t>56317</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>85605</t>
+          <t>84259</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3277,12 +3277,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>74176</t>
+          <t>74223</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>108128</t>
+          <t>108590</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3312,12 +3312,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,37%</t>
         </is>
       </c>
     </row>
@@ -3340,12 +3340,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>17560</t>
+          <t>17321</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>35546</t>
+          <t>35325</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,12 +3375,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>45999</t>
+          <t>45953</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>73873</t>
+          <t>73648</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3390,12 +3390,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,12 +3410,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>68120</t>
+          <t>68901</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>100743</t>
+          <t>101870</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3425,12 +3425,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,5%</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>5643</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,12 +3488,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11894</t>
+          <t>11614</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,12 +3523,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3573</t>
+          <t>3256</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13827</t>
+          <t>14253</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -3566,12 +3566,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8978</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>22788</t>
+          <t>22591</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3581,12 +3581,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,12 +3601,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>38499</t>
+          <t>38243</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>63705</t>
+          <t>63953</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,12 +3636,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>52046</t>
+          <t>52795</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>79541</t>
+          <t>80466</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>4599</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>17722</t>
+          <t>17041</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>4675</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>19014</t>
+          <t>18213</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>5621</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5596</t>
+          <t>5641</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5032</t>
+          <t>4728</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>6974</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -4365,12 +4365,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>951</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>7866</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4380,12 +4380,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>934</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>8328</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12215</t>
+          <t>12663</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -4478,12 +4478,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17787</t>
+          <t>17643</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32208</t>
+          <t>31744</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4493,12 +4493,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13166</t>
+          <t>12410</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29019</t>
+          <t>28011</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4548,12 +4548,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35160</t>
+          <t>34537</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57408</t>
+          <t>57239</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>49,7%</t>
         </is>
       </c>
     </row>
@@ -4591,12 +4591,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>1126</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12163</t>
+          <t>10374</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4606,12 +4606,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13162</t>
+          <t>13350</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28123</t>
+          <t>29004</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16477</t>
+          <t>16315</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>33399</t>
+          <t>34857</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>30,26%</t>
         </is>
       </c>
     </row>
@@ -4704,12 +4704,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11744</t>
+          <t>12136</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4719,12 +4719,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4739,12 +4739,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>13556</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27680</t>
+          <t>27933</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18414</t>
+          <t>17934</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36776</t>
+          <t>36986</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,11%</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11190</t>
+          <t>12112</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13356</t>
+          <t>13686</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -4930,12 +4930,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>963</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8567</t>
+          <t>8570</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -4965,12 +4965,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15029</t>
+          <t>14582</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4980,12 +4980,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5000,12 +5000,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5381</t>
+          <t>5739</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18146</t>
+          <t>19189</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5015,12 +5015,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7164</t>
+          <t>6395</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5078,12 +5078,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11237</t>
+          <t>12451</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5093,12 +5093,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5113,12 +5113,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>3808</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>14254</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5128,12 +5128,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -5387,7 +5387,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5055</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>4969</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13088</t>
+          <t>12214</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9146</t>
+          <t>10293</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5569,12 +5569,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3196</t>
+          <t>2254</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16054</t>
+          <t>16668</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5584,12 +5584,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -5612,12 +5612,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22952</t>
+          <t>23307</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>43601</t>
+          <t>44197</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5647,12 +5647,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14337</t>
+          <t>15132</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33835</t>
+          <t>32837</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5662,12 +5662,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>41906</t>
+          <t>42140</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>70955</t>
+          <t>70514</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5697,12 +5697,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -5725,12 +5725,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13295</t>
+          <t>13570</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30772</t>
+          <t>31903</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5760,12 +5760,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46882</t>
+          <t>48962</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75369</t>
+          <t>76980</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67460</t>
+          <t>67858</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>100338</t>
+          <t>98381</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>31,68%</t>
         </is>
       </c>
     </row>
@@ -5838,12 +5838,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19910</t>
+          <t>18386</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39442</t>
+          <t>36280</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>55900</t>
+          <t>54835</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>84228</t>
+          <t>82591</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>80500</t>
+          <t>79415</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>115362</t>
+          <t>112823</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,33%</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5662</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7286</t>
+          <t>6659</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8854</t>
+          <t>8711</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -6064,12 +6064,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10264</t>
+          <t>10373</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25758</t>
+          <t>25692</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6079,12 +6079,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27704</t>
+          <t>28226</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53136</t>
+          <t>52608</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6134,12 +6134,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44023</t>
+          <t>42825</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>71369</t>
+          <t>73706</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,74%</t>
         </is>
       </c>
     </row>
@@ -6177,12 +6177,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4482</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16633</t>
+          <t>17271</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34249</t>
+          <t>33379</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58833</t>
+          <t>58255</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>42501</t>
+          <t>43354</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>69512</t>
+          <t>70074</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,57%</t>
         </is>
       </c>
     </row>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>7657</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6630</t>
+          <t>6631</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -6633,12 +6633,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16193</t>
+          <t>15764</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6648,12 +6648,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6668,12 +6668,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2238</t>
+          <t>2280</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13353</t>
+          <t>13169</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6426</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>22914</t>
+          <t>23012</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -6746,12 +6746,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>44567</t>
+          <t>45161</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>69964</t>
+          <t>71663</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6781,12 +6781,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31763</t>
+          <t>31767</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>59367</t>
+          <t>56176</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>81765</t>
+          <t>82601</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>118811</t>
+          <t>119601</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,1%</t>
         </is>
       </c>
     </row>
@@ -6859,12 +6859,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17303</t>
+          <t>17651</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>37958</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>65884</t>
+          <t>66146</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>96460</t>
+          <t>98151</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>90556</t>
+          <t>89947</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>126274</t>
+          <t>126573</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,73%</t>
         </is>
       </c>
     </row>
@@ -6972,12 +6972,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>24159</t>
+          <t>23707</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>46071</t>
+          <t>45501</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7007,12 +7007,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>74063</t>
+          <t>73799</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>105453</t>
+          <t>105405</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>104150</t>
+          <t>103211</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>142057</t>
+          <t>142669</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,51%</t>
         </is>
       </c>
     </row>
@@ -7085,12 +7085,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14098</t>
+          <t>13502</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7105,7 +7105,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>985</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8357</t>
+          <t>8554</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3156</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>16662</t>
+          <t>16801</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -7198,12 +7198,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12907</t>
+          <t>12905</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>30208</t>
+          <t>30593</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>34794</t>
+          <t>34608</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>61431</t>
+          <t>60147</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>53131</t>
+          <t>50978</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>84693</t>
+          <t>83270</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7283,12 +7283,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,56%</t>
         </is>
       </c>
     </row>
@@ -7311,12 +7311,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6158</t>
+          <t>6405</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>20445</t>
+          <t>19858</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7326,12 +7326,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>39457</t>
+          <t>39427</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>67023</t>
+          <t>66518</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7361,12 +7361,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>49252</t>
+          <t>50132</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>79016</t>
+          <t>80908</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7396,12 +7396,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -7655,7 +7655,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4921</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>7711</t>
+          <t>7637</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7720,12 +7720,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>994</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>9523</t>
+          <t>10106</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -8002,7 +8002,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>6297</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6219</t>
+          <t>5971</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19058</t>
+          <t>18578</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6421</t>
+          <t>6240</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19920</t>
+          <t>20026</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -8110,12 +8110,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14729</t>
+          <t>14274</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25366</t>
+          <t>25174</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19091</t>
+          <t>19436</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37210</t>
+          <t>36921</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37520</t>
+          <t>37188</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58278</t>
+          <t>59475</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>52,41%</t>
         </is>
       </c>
     </row>
@@ -8223,12 +8223,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10106</t>
+          <t>10051</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8238,12 +8238,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9639</t>
+          <t>9791</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25174</t>
+          <t>25838</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13896</t>
+          <t>13640</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31410</t>
+          <t>31359</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,63%</t>
         </is>
       </c>
     </row>
@@ -8336,12 +8336,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11342</t>
+          <t>11375</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8510</t>
+          <t>9119</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23491</t>
+          <t>23131</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8386,12 +8386,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13327</t>
+          <t>13435</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30005</t>
+          <t>29246</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>25,77%</t>
         </is>
       </c>
     </row>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8049</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7205</t>
+          <t>8239</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>5268</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8582,42 +8582,42 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
+          <t>16,81%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>13594</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>7399</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>21690</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
           <t>16,55%</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>13594</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>7982</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>21115</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>16,55%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>8466</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>22521</t>
+          <t>23261</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,5%</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>4831</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8695,7 +8695,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9365</t>
+          <t>9410</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8730,7 +8730,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>962</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11184</t>
+          <t>9718</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8765,7 +8765,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -9136,7 +9136,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3249</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4894</t>
+          <t>5038</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18963</t>
+          <t>20549</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9181,12 +9181,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5867</t>
+          <t>5623</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22701</t>
+          <t>21342</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -9244,12 +9244,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24638</t>
+          <t>25186</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>41804</t>
+          <t>41230</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9259,12 +9259,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10464</t>
+          <t>10175</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30173</t>
+          <t>30287</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9294,12 +9294,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>40413</t>
+          <t>40237</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>65632</t>
+          <t>66627</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,2%</t>
         </is>
       </c>
     </row>
@@ -9357,12 +9357,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8373</t>
+          <t>8178</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20390</t>
+          <t>21260</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9372,12 +9372,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40734</t>
+          <t>41853</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67362</t>
+          <t>69437</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52597</t>
+          <t>52931</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84310</t>
+          <t>83142</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,2%</t>
         </is>
       </c>
     </row>
@@ -9470,12 +9470,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21561</t>
+          <t>22006</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38862</t>
+          <t>38376</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9485,12 +9485,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9505,12 +9505,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46513</t>
+          <t>46285</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>74859</t>
+          <t>73266</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>74149</t>
+          <t>73217</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>107754</t>
+          <t>107192</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>38,93%</t>
         </is>
       </c>
     </row>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5098</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9603,7 +9603,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1225</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12231</t>
+          <t>13302</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12650</t>
+          <t>12708</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -9696,12 +9696,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10703</t>
+          <t>11291</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24194</t>
+          <t>24243</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9711,12 +9711,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19246</t>
+          <t>18800</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43679</t>
+          <t>42470</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32667</t>
+          <t>33945</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59489</t>
+          <t>59804</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,72%</t>
         </is>
       </c>
     </row>
@@ -9809,12 +9809,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1673</t>
+          <t>1639</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9934</t>
+          <t>9753</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9824,12 +9824,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9844,12 +9844,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7810</t>
+          <t>8225</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>24066</t>
+          <t>24441</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9859,12 +9859,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12180</t>
+          <t>12141</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30572</t>
+          <t>30111</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6040</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6188</t>
+          <t>6729</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -10153,7 +10153,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10168,7 +10168,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10188,7 +10188,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8677</t>
+          <t>7543</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10218,12 +10218,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>776</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>9239</t>
+          <t>8895</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -10270,7 +10270,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6573</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10300,12 +10300,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14120</t>
+          <t>14223</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>33383</t>
+          <t>33820</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>14844</t>
+          <t>15546</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>35393</t>
+          <t>36057</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -10378,12 +10378,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>43323</t>
+          <t>44557</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>64488</t>
+          <t>64999</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10413,12 +10413,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>33670</t>
+          <t>34196</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>62436</t>
+          <t>60696</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10428,12 +10428,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10448,12 +10448,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>82445</t>
+          <t>81430</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>117938</t>
+          <t>119400</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10463,12 +10463,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,71%</t>
         </is>
       </c>
     </row>
@@ -10491,12 +10491,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12101</t>
+          <t>11535</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26920</t>
+          <t>26314</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10506,12 +10506,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10526,12 +10526,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>55599</t>
+          <t>57053</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>86891</t>
+          <t>88563</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10541,12 +10541,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>73146</t>
+          <t>72307</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>108127</t>
+          <t>107990</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,77%</t>
         </is>
       </c>
     </row>
@@ -10604,12 +10604,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>26582</t>
+          <t>26604</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>44854</t>
+          <t>44783</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10639,12 +10639,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>59795</t>
+          <t>59683</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>92871</t>
+          <t>92419</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10654,12 +10654,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>90859</t>
+          <t>90803</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>129260</t>
+          <t>128435</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10689,12 +10689,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,03%</t>
         </is>
       </c>
     </row>
@@ -10722,7 +10722,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6211</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10737,7 +10737,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2478</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>15565</t>
+          <t>14437</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10767,12 +10767,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3582</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>15803</t>
+          <t>16601</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10802,12 +10802,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -10830,12 +10830,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11444</t>
+          <t>11091</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26023</t>
+          <t>25643</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10845,12 +10845,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>30705</t>
+          <t>30741</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>59190</t>
+          <t>57077</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10880,12 +10880,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>45469</t>
+          <t>46327</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>75345</t>
+          <t>76812</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10915,12 +10915,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -10943,12 +10943,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11524</t>
+          <t>11702</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10958,12 +10958,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10978,12 +10978,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>9908</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>29027</t>
+          <t>28902</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10993,47 +10993,47 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>10,81%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>23364</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>14812</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>35603</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>6,01%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
           <t>3,81%</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>10,86%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>23364</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>14368</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>33654</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>6,01%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6863</t>
+          <t>7993</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11111,7 +11111,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11146,7 +11146,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -11287,7 +11287,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4848</t>
+          <t>4355</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11322,7 +11322,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>7990</t>
+          <t>8570</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11352,12 +11352,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>787</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>9479</t>
+          <t>9253</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11367,12 +11367,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -11624,32 +11624,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3618</t>
+          <t>3876</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7930</t>
+          <t>7668</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11659,32 +11659,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3694</t>
+          <t>3986</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11694,32 +11694,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>7862</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11937</t>
+          <t>12698</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -11737,32 +11737,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25589</t>
+          <t>28550</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19788</t>
+          <t>22447</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31407</t>
+          <t>34083</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11772,32 +11772,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17967</t>
+          <t>19644</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13429</t>
+          <t>13944</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23663</t>
+          <t>25768</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11807,32 +11807,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>43555</t>
+          <t>48195</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35565</t>
+          <t>39328</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52098</t>
+          <t>57036</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,07%</t>
         </is>
       </c>
     </row>
@@ -11850,27 +11850,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7046</t>
+          <t>8281</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3621</t>
+          <t>4109</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12533</t>
+          <t>13691</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -11885,32 +11885,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15218</t>
+          <t>17344</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10775</t>
+          <t>12547</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20243</t>
+          <t>23356</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11920,32 +11920,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>22264</t>
+          <t>25626</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16636</t>
+          <t>19024</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29370</t>
+          <t>33799</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,93%</t>
         </is>
       </c>
     </row>
@@ -11963,32 +11963,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19366</t>
+          <t>20550</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14175</t>
+          <t>15220</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25237</t>
+          <t>26802</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11998,32 +11998,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>40036</t>
+          <t>43430</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34202</t>
+          <t>36890</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46297</t>
+          <t>50169</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12033,32 +12033,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>59402</t>
+          <t>63980</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51534</t>
+          <t>54810</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68248</t>
+          <t>72767</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>53,67%</t>
         </is>
       </c>
     </row>
@@ -12076,32 +12076,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4415</t>
+          <t>4586</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9285</t>
+          <t>9151</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12111,32 +12111,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6089</t>
+          <t>6632</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>3560</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10327</t>
+          <t>11292</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12146,32 +12146,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>11218</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6553</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15848</t>
+          <t>16696</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,31%</t>
         </is>
       </c>
     </row>
@@ -12189,32 +12189,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>7525</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t>3907</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11673</t>
+          <t>12959</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12224,32 +12224,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9558</t>
+          <t>10209</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5979</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14303</t>
+          <t>15005</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -12259,32 +12259,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>16414</t>
+          <t>17735</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11072</t>
+          <t>12635</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>22619</t>
+          <t>24188</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -12302,32 +12302,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3375</t>
+          <t>3452</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>7043</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12337,32 +12337,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9663</t>
+          <t>11428</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>7519</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14618</t>
+          <t>17442</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12372,32 +12372,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>13038</t>
+          <t>14880</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8679</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18709</t>
+          <t>20991</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -12450,7 +12450,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>677</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2967</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -12475,7 +12475,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12485,7 +12485,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>677</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -12495,12 +12495,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3559</t>
+          <t>3412</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -12641,7 +12641,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>609</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -12651,12 +12651,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3145</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -12666,7 +12666,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>569</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -12686,12 +12686,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -12701,7 +12701,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12711,7 +12711,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -12721,12 +12721,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3969</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -12758,22 +12758,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>2272</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8833</t>
+          <t>10112</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -12783,7 +12783,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12793,32 +12793,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>11030</t>
+          <t>12346</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7175</t>
+          <t>7478</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16580</t>
+          <t>18085</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12828,32 +12828,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>15811</t>
+          <t>17554</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10892</t>
+          <t>12331</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22437</t>
+          <t>24377</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -12871,32 +12871,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30604</t>
+          <t>33205</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24297</t>
+          <t>25042</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38952</t>
+          <t>41220</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12906,32 +12906,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21507</t>
+          <t>24541</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16270</t>
+          <t>18160</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28523</t>
+          <t>32358</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12941,32 +12941,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>52111</t>
+          <t>57746</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>42870</t>
+          <t>47850</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>63558</t>
+          <t>68995</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,66%</t>
         </is>
       </c>
     </row>
@@ -12984,32 +12984,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9934</t>
+          <t>10203</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>5997</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15504</t>
+          <t>15772</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13019,32 +13019,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>50445</t>
+          <t>54573</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41616</t>
+          <t>45458</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59995</t>
+          <t>65283</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13054,32 +13054,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>60379</t>
+          <t>64776</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>50554</t>
+          <t>53969</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72108</t>
+          <t>76371</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -13097,32 +13097,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>60727</t>
+          <t>63897</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>52552</t>
+          <t>55137</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>68391</t>
+          <t>72518</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>63,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13132,32 +13132,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>152172</t>
+          <t>162116</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>140625</t>
+          <t>150380</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>163590</t>
+          <t>173798</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13167,32 +13167,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>212899</t>
+          <t>226013</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>198919</t>
+          <t>210116</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>226215</t>
+          <t>240576</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>61,56%</t>
         </is>
       </c>
     </row>
@@ -13210,32 +13210,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3136</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7145</t>
+          <t>7045</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13245,32 +13245,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11075</t>
+          <t>12247</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6915</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17647</t>
+          <t>19163</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13280,32 +13280,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>14211</t>
+          <t>15222</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9380</t>
+          <t>9953</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20680</t>
+          <t>22486</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -13323,32 +13323,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18355</t>
+          <t>19467</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12774</t>
+          <t>13465</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25128</t>
+          <t>26201</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13358,32 +13358,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>50442</t>
+          <t>55370</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42017</t>
+          <t>45631</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>60960</t>
+          <t>66793</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13393,32 +13393,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>68797</t>
+          <t>74837</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>57756</t>
+          <t>62759</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>80822</t>
+          <t>87313</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -13436,32 +13436,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>25173</t>
+          <t>27284</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18901</t>
+          <t>20222</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32567</t>
+          <t>35969</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13471,32 +13471,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>71089</t>
+          <t>75419</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>62349</t>
+          <t>64379</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>82588</t>
+          <t>86786</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13506,32 +13506,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>96261</t>
+          <t>102703</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>85326</t>
+          <t>90532</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>107957</t>
+          <t>116795</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,89%</t>
         </is>
       </c>
     </row>
@@ -13549,7 +13549,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -13559,12 +13559,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3309</t>
+          <t>3534</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -13584,22 +13584,22 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1639</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>465</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4484</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13619,32 +13619,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2574</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>6210</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>600</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -13687,7 +13687,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13697,7 +13697,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>688</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -13707,12 +13707,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>3947</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -13722,7 +13722,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -13742,12 +13742,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4319</t>
+          <t>4435</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -13757,7 +13757,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -13775,7 +13775,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -13785,12 +13785,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>4964</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -13800,7 +13800,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13810,7 +13810,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>501</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -13820,7 +13820,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2397</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13835,7 +13835,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13845,32 +13845,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1889</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>5019</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -13892,32 +13892,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>8399</t>
+          <t>9085</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4722</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14007</t>
+          <t>14989</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13927,32 +13927,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>14724</t>
+          <t>16332</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10871</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>23262</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13962,32 +13962,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>23124</t>
+          <t>25416</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16054</t>
+          <t>19009</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>30365</t>
+          <t>34345</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -14005,32 +14005,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>56193</t>
+          <t>61755</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>46020</t>
+          <t>52421</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>66350</t>
+          <t>72556</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14040,32 +14040,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>39474</t>
+          <t>44186</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31765</t>
+          <t>36380</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>47763</t>
+          <t>54257</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14075,32 +14075,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>95666</t>
+          <t>105940</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>84524</t>
+          <t>92447</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>109498</t>
+          <t>121905</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -14118,32 +14118,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>16980</t>
+          <t>18484</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11073</t>
+          <t>12401</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23212</t>
+          <t>25873</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14153,67 +14153,67 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>65663</t>
+          <t>71918</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>56376</t>
+          <t>60645</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>76944</t>
+          <t>84124</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
+          <t>20,13%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>16,98%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>23,55%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>90402</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>79288</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>105282</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>17,17%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>15,06%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>20,0%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>17,17%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>23,44%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>82643</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>71176</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>96198</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>17,03%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>14,67%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -14231,32 +14231,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>80093</t>
+          <t>84447</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>70318</t>
+          <t>73721</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>89567</t>
+          <t>94448</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -14266,32 +14266,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>192209</t>
+          <t>205546</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>178607</t>
+          <t>191431</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>204104</t>
+          <t>218341</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -14301,32 +14301,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>272302</t>
+          <t>289993</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>256200</t>
+          <t>271305</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>288244</t>
+          <t>306124</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>58,16%</t>
         </is>
       </c>
     </row>
@@ -14344,32 +14344,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>7551</t>
+          <t>7561</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3890</t>
+          <t>4040</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12919</t>
+          <t>12583</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14379,32 +14379,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>17165</t>
+          <t>18879</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>11911</t>
+          <t>13233</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>24099</t>
+          <t>26954</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14414,32 +14414,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>24716</t>
+          <t>26440</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>18037</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>33050</t>
+          <t>35462</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -14457,32 +14457,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>25211</t>
+          <t>26992</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>18667</t>
+          <t>20002</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>33011</t>
+          <t>35469</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14492,32 +14492,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>65579</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>50322</t>
+          <t>55390</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>71059</t>
+          <t>77733</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14527,32 +14527,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>85211</t>
+          <t>92571</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>74166</t>
+          <t>79630</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>97772</t>
+          <t>106687</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,27%</t>
         </is>
       </c>
     </row>
@@ -14570,17 +14570,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>28548</t>
+          <t>30736</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22056</t>
+          <t>23183</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>37927</t>
+          <t>40028</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14590,12 +14590,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14605,32 +14605,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>80752</t>
+          <t>86848</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>69568</t>
+          <t>76206</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>92229</t>
+          <t>98127</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14640,22 +14640,22 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>109300</t>
+          <t>117584</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>96424</t>
+          <t>104581</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>123491</t>
+          <t>133084</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,28%</t>
         </is>
       </c>
     </row>
@@ -14683,7 +14683,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -14693,12 +14693,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3193</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -14708,7 +14708,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14718,32 +14718,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>2227</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>732</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>5652</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14753,17 +14753,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>3162</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6715</t>
+          <t>6840</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14773,12 +14773,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>600</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -14806,12 +14806,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -14821,7 +14821,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14831,7 +14831,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>688</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -14841,7 +14841,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3488</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14856,7 +14856,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14866,7 +14866,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -14876,12 +14876,12 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3717</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -14891,7 +14891,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -14909,32 +14909,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>612</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>5364</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -14944,7 +14944,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -14954,12 +14954,12 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>4036</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -14969,7 +14969,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -14979,32 +14979,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>3051</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>6665</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
